--- a/docs/Drakens_Energy_360_Report.xlsx
+++ b/docs/Drakens_Energy_360_Report.xlsx
@@ -74,7 +74,7 @@
     <t>Provinces</t>
   </si>
   <si>
-    <t>2026-09-07</t>
+    <t>2026-09-08</t>
   </si>
   <si>
     <t>drakens360_test_full.duckdb</t>
@@ -656,15 +656,15 @@
     <t>qualifying_spend_zar_non_negative</t>
   </si>
   <si>
+    <t>customer_id_present</t>
+  </si>
+  <si>
+    <t>volume_litres_non_negative</t>
+  </si>
+  <si>
     <t>credit_amount_zar_non_negative</t>
   </si>
   <si>
-    <t>volume_litres_non_negative</t>
-  </si>
-  <si>
-    <t>customer_id_present</t>
-  </si>
-  <si>
     <t>capacity_litres_non_negative</t>
   </si>
   <si>
@@ -710,18 +710,18 @@
     <t>total_cost_zar_non_negative</t>
   </si>
   <si>
+    <t>rated_power_kw_non_negative</t>
+  </si>
+  <si>
     <t>labour_cost_zar_non_negative</t>
   </si>
   <si>
-    <t>rated_power_kw_non_negative</t>
+    <t>parts_cost_zar_non_negative</t>
   </si>
   <si>
     <t>average_power_kw_non_negative</t>
   </si>
   <si>
-    <t>parts_cost_zar_non_negative</t>
-  </si>
-  <si>
     <t>incident_id_present</t>
   </si>
   <si>
@@ -830,7 +830,7 @@
     <t>Transactions</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>Outside South Africa</t>
   </si>
   <si>
     <t>Gauteng</t>
@@ -6404,10 +6404,10 @@
         <v>205</v>
       </c>
       <c r="B31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C31" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D31">
         <v>88</v>
@@ -6432,10 +6432,10 @@
         <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C33" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D33">
         <v>88</v>
@@ -6875,7 +6875,7 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" customWidth="1"/>

--- a/docs/Drakens_Energy_360_Report.xlsx
+++ b/docs/Drakens_Energy_360_Report.xlsx
@@ -647,21 +647,21 @@
     <t>debit_amount_zar_non_negative</t>
   </si>
   <si>
+    <t>solar_reading_id_present</t>
+  </si>
+  <si>
     <t>order_id_present</t>
   </si>
   <si>
-    <t>solar_reading_id_present</t>
-  </si>
-  <si>
     <t>qualifying_spend_zar_non_negative</t>
   </si>
   <si>
+    <t>volume_litres_non_negative</t>
+  </si>
+  <si>
     <t>customer_id_present</t>
   </si>
   <si>
-    <t>volume_litres_non_negative</t>
-  </si>
-  <si>
     <t>credit_amount_zar_non_negative</t>
   </si>
   <si>
@@ -701,25 +701,25 @@
     <t>delivered_litres_within_range</t>
   </si>
   <si>
+    <t>work_order_id_present</t>
+  </si>
+  <si>
     <t>grid_cost_zar_non_negative</t>
   </si>
   <si>
-    <t>work_order_id_present</t>
+    <t>rated_power_kw_non_negative</t>
+  </si>
+  <si>
+    <t>labour_cost_zar_non_negative</t>
   </si>
   <si>
     <t>total_cost_zar_non_negative</t>
   </si>
   <si>
-    <t>rated_power_kw_non_negative</t>
-  </si>
-  <si>
-    <t>labour_cost_zar_non_negative</t>
+    <t>average_power_kw_non_negative</t>
   </si>
   <si>
     <t>parts_cost_zar_non_negative</t>
-  </si>
-  <si>
-    <t>average_power_kw_non_negative</t>
   </si>
   <si>
     <t>incident_id_present</t>
@@ -6404,10 +6404,10 @@
         <v>205</v>
       </c>
       <c r="B31" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C31" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D31">
         <v>88</v>
@@ -6418,10 +6418,10 @@
         <v>206</v>
       </c>
       <c r="B32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C32" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D32">
         <v>88</v>
@@ -6614,10 +6614,10 @@
         <v>220</v>
       </c>
       <c r="B46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C46" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D46">
         <v>8</v>
@@ -6628,10 +6628,10 @@
         <v>221</v>
       </c>
       <c r="B47" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C47" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D47">
         <v>8</v>

--- a/docs/Drakens_Energy_360_Report.xlsx
+++ b/docs/Drakens_Energy_360_Report.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Investment by province'!$A$4:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Investment plan'!$A$4:$O$753</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Limitations!$A$4:$A$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'ML results'!$A$4:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'ML results'!$A$4:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Province!$A$4:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Quarantine!$A$4:$D$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$4:$B$11</definedName>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5300" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5306" uniqueCount="870">
   <si>
     <t>Drakens Energy 360 — Summary</t>
   </si>
@@ -659,24 +659,24 @@
     <t>debit_amount_zar_non_negative</t>
   </si>
   <si>
+    <t>solar_reading_id_present</t>
+  </si>
+  <si>
     <t>order_id_present</t>
   </si>
   <si>
-    <t>solar_reading_id_present</t>
-  </si>
-  <si>
     <t>qualifying_spend_zar_non_negative</t>
   </si>
   <si>
+    <t>credit_amount_zar_non_negative</t>
+  </si>
+  <si>
+    <t>volume_litres_non_negative</t>
+  </si>
+  <si>
     <t>customer_id_present</t>
   </si>
   <si>
-    <t>volume_litres_non_negative</t>
-  </si>
-  <si>
-    <t>credit_amount_zar_non_negative</t>
-  </si>
-  <si>
     <t>capacity_litres_non_negative</t>
   </si>
   <si>
@@ -713,27 +713,27 @@
     <t>delivered_litres_within_range</t>
   </si>
   <si>
+    <t>work_order_id_present</t>
+  </si>
+  <si>
     <t>grid_cost_zar_non_negative</t>
   </si>
   <si>
-    <t>work_order_id_present</t>
+    <t>labour_cost_zar_non_negative</t>
+  </si>
+  <si>
+    <t>total_cost_zar_non_negative</t>
   </si>
   <si>
     <t>rated_power_kw_non_negative</t>
   </si>
   <si>
-    <t>total_cost_zar_non_negative</t>
-  </si>
-  <si>
-    <t>labour_cost_zar_non_negative</t>
+    <t>average_power_kw_non_negative</t>
   </si>
   <si>
     <t>parts_cost_zar_non_negative</t>
   </si>
   <si>
-    <t>average_power_kw_non_negative</t>
-  </si>
-  <si>
     <t>incident_id_present</t>
   </si>
   <si>
@@ -2504,6 +2504,12 @@
     <t>Fraud Anomaly</t>
   </si>
   <si>
+    <t>Product Demand Forecast</t>
+  </si>
+  <si>
+    <t>Product Revenue Forecast 12M</t>
+  </si>
+  <si>
     <t>customer_churn</t>
   </si>
   <si>
@@ -2520,6 +2526,12 @@
   </si>
   <si>
     <t>fraud_anomaly</t>
+  </si>
+  <si>
+    <t>product_demand_forecast</t>
+  </si>
+  <si>
+    <t>product_revenue_forecast_12m</t>
   </si>
   <si>
     <t>roc_auc</t>
@@ -3391,9 +3403,9 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>'ML results'!$A$5:$A$10</c:f>
+              <c:f>'ML results'!$A$5:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>Customer Churn</c:v>
                 </c:pt>
@@ -3412,15 +3424,21 @@
                 <c:pt idx="5">
                   <c:v>Fraud Anomaly</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>Product Demand Forecast</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Product Revenue Forecast 12M</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'ML results'!$G$5:$G$10</c:f>
+              <c:f>'ML results'!$G$5:$G$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0.335747</c:v>
                 </c:pt>
@@ -3599,13 +3617,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1200150</xdr:colOff>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4024,10 +4042,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="24.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="27.7109375" style="1" customWidth="1"/>
@@ -4084,16 +4102,16 @@
         <v>811</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D5" s="5">
         <v>0.835747</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="F5" s="5">
         <v>0.5</v>
@@ -4102,7 +4120,7 @@
         <v>0.335747</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4110,16 +4128,16 @@
         <v>812</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D6" s="5">
         <v>40.75741</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="F6" s="5">
         <v>56.155097</v>
@@ -4128,7 +4146,7 @@
         <v>-15.397686</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4136,16 +4154,16 @@
         <v>813</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D7" s="5">
         <v>0.584792</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="F7" s="5">
         <v>0.5</v>
@@ -4154,7 +4172,7 @@
         <v>0.08479200000000001</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4162,16 +4180,16 @@
         <v>814</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D8" s="5">
         <v>0.615642</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F8" s="5">
         <v>0.619983</v>
@@ -4180,7 +4198,7 @@
         <v>-0.00434</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4188,16 +4206,16 @@
         <v>815</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D9" s="5">
         <v>0.501295</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="F9" s="5">
         <v>0.5</v>
@@ -4206,7 +4224,7 @@
         <v>0.001295</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4214,18 +4232,40 @@
         <v>816</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>831</v>
+        <v>835</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>835</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H10"/>
+  <autoFilter ref="A4:H12"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H10">
+  <conditionalFormatting sqref="A5:H12">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -4253,7 +4293,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="34" customHeight="1">
@@ -4266,106 +4306,106 @@
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
     </row>
   </sheetData>
@@ -4400,7 +4440,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="34" customHeight="1">
@@ -4413,32 +4453,32 @@
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
     </row>
   </sheetData>
@@ -7559,10 +7599,10 @@
         <v>205</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D31" s="5">
         <v>88</v>
@@ -7587,10 +7627,10 @@
         <v>207</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D33" s="5">
         <v>88</v>
@@ -7769,10 +7809,10 @@
         <v>220</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D46" s="5">
         <v>8</v>
@@ -7783,10 +7823,10 @@
         <v>221</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D47" s="5">
         <v>8</v>

--- a/docs/Drakens_Energy_360_Report.xlsx
+++ b/docs/Drakens_Energy_360_Report.xlsx
@@ -86,7 +86,7 @@
     <t>Provinces</t>
   </si>
   <si>
-    <t>2026-09-08</t>
+    <t>2026-09-09</t>
   </si>
   <si>
     <t>drakens360_test_full.duckdb</t>
@@ -719,13 +719,13 @@
     <t>grid_cost_zar_non_negative</t>
   </si>
   <si>
+    <t>rated_power_kw_non_negative</t>
+  </si>
+  <si>
     <t>labour_cost_zar_non_negative</t>
   </si>
   <si>
     <t>total_cost_zar_non_negative</t>
-  </si>
-  <si>
-    <t>rated_power_kw_non_negative</t>
   </si>
   <si>
     <t>average_power_kw_non_negative</t>

--- a/docs/Drakens_Energy_360_Report.xlsx
+++ b/docs/Drakens_Energy_360_Report.xlsx
@@ -659,24 +659,24 @@
     <t>debit_amount_zar_non_negative</t>
   </si>
   <si>
+    <t>order_id_present</t>
+  </si>
+  <si>
     <t>solar_reading_id_present</t>
   </si>
   <si>
-    <t>order_id_present</t>
-  </si>
-  <si>
     <t>qualifying_spend_zar_non_negative</t>
   </si>
   <si>
     <t>credit_amount_zar_non_negative</t>
   </si>
   <si>
+    <t>customer_id_present</t>
+  </si>
+  <si>
     <t>volume_litres_non_negative</t>
   </si>
   <si>
-    <t>customer_id_present</t>
-  </si>
-  <si>
     <t>capacity_litres_non_negative</t>
   </si>
   <si>
@@ -719,13 +719,13 @@
     <t>grid_cost_zar_non_negative</t>
   </si>
   <si>
+    <t>total_cost_zar_non_negative</t>
+  </si>
+  <si>
+    <t>labour_cost_zar_non_negative</t>
+  </si>
+  <si>
     <t>rated_power_kw_non_negative</t>
-  </si>
-  <si>
-    <t>labour_cost_zar_non_negative</t>
-  </si>
-  <si>
-    <t>total_cost_zar_non_negative</t>
   </si>
   <si>
     <t>average_power_kw_non_negative</t>
@@ -7613,10 +7613,10 @@
         <v>206</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D32" s="5">
         <v>88</v>
@@ -7627,10 +7627,10 @@
         <v>207</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D33" s="5">
         <v>88</v>
